--- a/artfynd/A 51945-2022 artfynd.xlsx
+++ b/artfynd/A 51945-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356484</v>
+        <v>113356288</v>
       </c>
       <c r="B2" t="n">
-        <v>96261</v>
+        <v>90727</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>749552</v>
+        <v>749589</v>
       </c>
       <c r="R2" t="n">
-        <v>7194775</v>
+        <v>7194789</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>113356593</v>
       </c>
       <c r="B3" t="n">
-        <v>96255</v>
+        <v>96271</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356288</v>
+        <v>113356449</v>
       </c>
       <c r="B4" t="n">
-        <v>90711</v>
+        <v>96277</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749589</v>
+        <v>749039</v>
       </c>
       <c r="R4" t="n">
-        <v>7194789</v>
+        <v>7194846</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Dahlin</t>
+          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356449</v>
+        <v>113356484</v>
       </c>
       <c r="B5" t="n">
-        <v>96261</v>
+        <v>96277</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749039</v>
+        <v>749552</v>
       </c>
       <c r="R5" t="n">
-        <v>7194846</v>
+        <v>7194775</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
+          <t>Johanna Kühne, Anna Dahlin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 51945-2022 artfynd.xlsx
+++ b/artfynd/A 51945-2022 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356593</v>
+        <v>113356449</v>
       </c>
       <c r="B3" t="n">
-        <v>96271</v>
+        <v>96277</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,19 +797,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221944</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -817,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749577</v>
+        <v>749039</v>
       </c>
       <c r="R3" t="n">
-        <v>7194739</v>
+        <v>7194846</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356449</v>
+        <v>113356593</v>
       </c>
       <c r="B4" t="n">
-        <v>96277</v>
+        <v>96271</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,23 +903,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749039</v>
+        <v>749577</v>
       </c>
       <c r="R4" t="n">
-        <v>7194846</v>
+        <v>7194739</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 51945-2022 artfynd.xlsx
+++ b/artfynd/A 51945-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356288</v>
+        <v>113356449</v>
       </c>
       <c r="B2" t="n">
-        <v>90727</v>
+        <v>96289</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>749589</v>
+        <v>749039</v>
       </c>
       <c r="R2" t="n">
-        <v>7194789</v>
+        <v>7194846</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Dahlin</t>
+          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356449</v>
+        <v>113356484</v>
       </c>
       <c r="B3" t="n">
-        <v>96277</v>
+        <v>96289</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749039</v>
+        <v>749552</v>
       </c>
       <c r="R3" t="n">
-        <v>7194846</v>
+        <v>7194775</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
+          <t>Johanna Kühne, Anna Dahlin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -890,7 +890,7 @@
         <v>113356593</v>
       </c>
       <c r="B4" t="n">
-        <v>96271</v>
+        <v>96283</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356484</v>
+        <v>113356288</v>
       </c>
       <c r="B5" t="n">
-        <v>96277</v>
+        <v>90739</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749552</v>
+        <v>749589</v>
       </c>
       <c r="R5" t="n">
-        <v>7194775</v>
+        <v>7194789</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 51945-2022 artfynd.xlsx
+++ b/artfynd/A 51945-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356449</v>
+        <v>113356288</v>
       </c>
       <c r="B2" t="n">
-        <v>96289</v>
+        <v>90739</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>749039</v>
+        <v>749589</v>
       </c>
       <c r="R2" t="n">
-        <v>7194846</v>
+        <v>7194789</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
+          <t>Johanna Kühne, Anna Dahlin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356288</v>
+        <v>113356449</v>
       </c>
       <c r="B5" t="n">
-        <v>90739</v>
+        <v>96289</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749589</v>
+        <v>749039</v>
       </c>
       <c r="R5" t="n">
-        <v>7194789</v>
+        <v>7194846</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Dahlin</t>
+          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 51945-2022 artfynd.xlsx
+++ b/artfynd/A 51945-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>113356288</v>
       </c>
       <c r="B2" t="n">
-        <v>90739</v>
+        <v>90761</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356484</v>
+        <v>113356593</v>
       </c>
       <c r="B3" t="n">
-        <v>96289</v>
+        <v>96305</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,23 +797,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -821,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749552</v>
+        <v>749577</v>
       </c>
       <c r="R3" t="n">
-        <v>7194775</v>
+        <v>7194739</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Dahlin</t>
+          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356593</v>
+        <v>113356449</v>
       </c>
       <c r="B4" t="n">
-        <v>96283</v>
+        <v>96311</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,19 +899,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221944</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749577</v>
+        <v>749039</v>
       </c>
       <c r="R4" t="n">
-        <v>7194739</v>
+        <v>7194846</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356449</v>
+        <v>113356484</v>
       </c>
       <c r="B5" t="n">
-        <v>96289</v>
+        <v>96311</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749039</v>
+        <v>749552</v>
       </c>
       <c r="R5" t="n">
-        <v>7194846</v>
+        <v>7194775</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
+          <t>Johanna Kühne, Anna Dahlin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 51945-2022 artfynd.xlsx
+++ b/artfynd/A 51945-2022 artfynd.xlsx
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356593</v>
+        <v>113356449</v>
       </c>
       <c r="B3" t="n">
-        <v>96305</v>
+        <v>96311</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,19 +797,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221944</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -817,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749577</v>
+        <v>749039</v>
       </c>
       <c r="R3" t="n">
-        <v>7194739</v>
+        <v>7194846</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356449</v>
+        <v>113356593</v>
       </c>
       <c r="B4" t="n">
-        <v>96311</v>
+        <v>96305</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,23 +903,19 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749039</v>
+        <v>749577</v>
       </c>
       <c r="R4" t="n">
-        <v>7194846</v>
+        <v>7194739</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>

--- a/artfynd/A 51945-2022 artfynd.xlsx
+++ b/artfynd/A 51945-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356288</v>
+        <v>113356484</v>
       </c>
       <c r="B2" t="n">
-        <v>90761</v>
+        <v>96315</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>749589</v>
+        <v>749552</v>
       </c>
       <c r="R2" t="n">
-        <v>7194789</v>
+        <v>7194775</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -784,7 +784,7 @@
         <v>113356449</v>
       </c>
       <c r="B3" t="n">
-        <v>96311</v>
+        <v>96315</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>113356593</v>
       </c>
       <c r="B4" t="n">
-        <v>96305</v>
+        <v>96309</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356484</v>
+        <v>113356288</v>
       </c>
       <c r="B5" t="n">
-        <v>96311</v>
+        <v>90765</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749552</v>
+        <v>749589</v>
       </c>
       <c r="R5" t="n">
-        <v>7194775</v>
+        <v>7194789</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 51945-2022 artfynd.xlsx
+++ b/artfynd/A 51945-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356484</v>
+        <v>113356593</v>
       </c>
       <c r="B2" t="n">
-        <v>96315</v>
+        <v>96309</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,23 +691,19 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -715,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>749552</v>
+        <v>749577</v>
       </c>
       <c r="R2" t="n">
-        <v>7194775</v>
+        <v>7194739</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +766,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Dahlin</t>
+          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356449</v>
+        <v>113356288</v>
       </c>
       <c r="B3" t="n">
-        <v>96315</v>
+        <v>90765</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749039</v>
+        <v>749589</v>
       </c>
       <c r="R3" t="n">
-        <v>7194846</v>
+        <v>7194789</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
+          <t>Johanna Kühne, Anna Dahlin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356593</v>
+        <v>113356449</v>
       </c>
       <c r="B4" t="n">
-        <v>96309</v>
+        <v>96315</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,19 +899,23 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221944</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749577</v>
+        <v>749039</v>
       </c>
       <c r="R4" t="n">
-        <v>7194739</v>
+        <v>7194846</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356288</v>
+        <v>113356484</v>
       </c>
       <c r="B5" t="n">
-        <v>90765</v>
+        <v>96315</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749589</v>
+        <v>749552</v>
       </c>
       <c r="R5" t="n">
-        <v>7194789</v>
+        <v>7194775</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 51945-2022 artfynd.xlsx
+++ b/artfynd/A 51945-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356593</v>
+        <v>113356449</v>
       </c>
       <c r="B2" t="n">
-        <v>96309</v>
+        <v>96321</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,19 +691,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221944</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -711,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>749577</v>
+        <v>749039</v>
       </c>
       <c r="R2" t="n">
-        <v>7194739</v>
+        <v>7194846</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356288</v>
+        <v>113356593</v>
       </c>
       <c r="B3" t="n">
-        <v>90765</v>
+        <v>96315</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,23 +797,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>221944</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749589</v>
+        <v>749577</v>
       </c>
       <c r="R3" t="n">
-        <v>7194789</v>
+        <v>7194739</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Dahlin</t>
+          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356449</v>
+        <v>113356484</v>
       </c>
       <c r="B4" t="n">
-        <v>96315</v>
+        <v>96321</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749039</v>
+        <v>749552</v>
       </c>
       <c r="R4" t="n">
-        <v>7194846</v>
+        <v>7194775</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
+          <t>Johanna Kühne, Anna Dahlin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356484</v>
+        <v>113356288</v>
       </c>
       <c r="B5" t="n">
-        <v>96315</v>
+        <v>90771</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,21 +1005,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749552</v>
+        <v>749589</v>
       </c>
       <c r="R5" t="n">
-        <v>7194775</v>
+        <v>7194789</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>

--- a/artfynd/A 51945-2022 artfynd.xlsx
+++ b/artfynd/A 51945-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356449</v>
+        <v>113356288</v>
       </c>
       <c r="B2" t="n">
-        <v>96321</v>
+        <v>90771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>749039</v>
+        <v>749589</v>
       </c>
       <c r="R2" t="n">
-        <v>7194846</v>
+        <v>7194789</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
+          <t>Johanna Kühne, Anna Dahlin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356593</v>
+        <v>113356449</v>
       </c>
       <c r="B3" t="n">
-        <v>96315</v>
+        <v>96321</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,19 +797,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221944</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -817,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749577</v>
+        <v>749039</v>
       </c>
       <c r="R3" t="n">
-        <v>7194739</v>
+        <v>7194846</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -989,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356288</v>
+        <v>113356593</v>
       </c>
       <c r="B5" t="n">
-        <v>90771</v>
+        <v>96315</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,23 +1009,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>3298</v>
+        <v>221944</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749589</v>
+        <v>749577</v>
       </c>
       <c r="R5" t="n">
-        <v>7194789</v>
+        <v>7194739</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Dahlin</t>
+          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 51945-2022 artfynd.xlsx
+++ b/artfynd/A 51945-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356288</v>
+        <v>113356484</v>
       </c>
       <c r="B2" t="n">
-        <v>90771</v>
+        <v>96328</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>749589</v>
+        <v>749552</v>
       </c>
       <c r="R2" t="n">
-        <v>7194789</v>
+        <v>7194775</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356449</v>
+        <v>113356288</v>
       </c>
       <c r="B3" t="n">
-        <v>96321</v>
+        <v>90778</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,21 +797,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749039</v>
+        <v>749589</v>
       </c>
       <c r="R3" t="n">
-        <v>7194846</v>
+        <v>7194789</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
+          <t>Johanna Kühne, Anna Dahlin</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -887,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356484</v>
+        <v>113356449</v>
       </c>
       <c r="B4" t="n">
-        <v>96321</v>
+        <v>96328</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749552</v>
+        <v>749039</v>
       </c>
       <c r="R4" t="n">
-        <v>7194775</v>
+        <v>7194846</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Dahlin</t>
+          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -996,7 +996,7 @@
         <v>113356593</v>
       </c>
       <c r="B5" t="n">
-        <v>96315</v>
+        <v>96322</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 51945-2022 artfynd.xlsx
+++ b/artfynd/A 51945-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356484</v>
+        <v>113356288</v>
       </c>
       <c r="B2" t="n">
-        <v>96328</v>
+        <v>90783</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>749552</v>
+        <v>749589</v>
       </c>
       <c r="R2" t="n">
-        <v>7194775</v>
+        <v>7194789</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356288</v>
+        <v>113356593</v>
       </c>
       <c r="B3" t="n">
-        <v>90778</v>
+        <v>96327</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,23 +797,19 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>3298</v>
+        <v>221944</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -821,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749589</v>
+        <v>749577</v>
       </c>
       <c r="R3" t="n">
-        <v>7194789</v>
+        <v>7194739</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +872,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Dahlin</t>
+          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -890,7 +886,7 @@
         <v>113356449</v>
       </c>
       <c r="B4" t="n">
-        <v>96328</v>
+        <v>96333</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -993,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356593</v>
+        <v>113356484</v>
       </c>
       <c r="B5" t="n">
-        <v>96322</v>
+        <v>96333</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,19 +1005,23 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221944</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749577</v>
+        <v>749552</v>
       </c>
       <c r="R5" t="n">
-        <v>7194739</v>
+        <v>7194775</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
+          <t>Johanna Kühne, Anna Dahlin</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 51945-2022 artfynd.xlsx
+++ b/artfynd/A 51945-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356288</v>
+        <v>113356449</v>
       </c>
       <c r="B2" t="n">
-        <v>90783</v>
+        <v>96361</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3298</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>749589</v>
+        <v>749039</v>
       </c>
       <c r="R2" t="n">
-        <v>7194789</v>
+        <v>7194846</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Dahlin</t>
+          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -784,7 +784,7 @@
         <v>113356593</v>
       </c>
       <c r="B3" t="n">
-        <v>96327</v>
+        <v>96355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356449</v>
+        <v>113356288</v>
       </c>
       <c r="B4" t="n">
-        <v>96333</v>
+        <v>90814</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,21 +899,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749039</v>
+        <v>749589</v>
       </c>
       <c r="R4" t="n">
-        <v>7194846</v>
+        <v>7194789</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -978,7 +978,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
+          <t>Johanna Kühne, Anna Dahlin</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -992,7 +992,7 @@
         <v>113356484</v>
       </c>
       <c r="B5" t="n">
-        <v>96333</v>
+        <v>96361</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>

--- a/artfynd/A 51945-2022 artfynd.xlsx
+++ b/artfynd/A 51945-2022 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113356449</v>
+        <v>113356288</v>
       </c>
       <c r="B2" t="n">
-        <v>96361</v>
+        <v>90815</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>3298</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>749039</v>
+        <v>749589</v>
       </c>
       <c r="R2" t="n">
-        <v>7194846</v>
+        <v>7194789</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
+          <t>Johanna Kühne, Anna Dahlin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113356593</v>
+        <v>113356449</v>
       </c>
       <c r="B3" t="n">
-        <v>96355</v>
+        <v>96361</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,19 +797,23 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221944</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lopplummer (aggregat)</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Huperzia selago agg.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -817,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>749577</v>
+        <v>749039</v>
       </c>
       <c r="R3" t="n">
-        <v>7194739</v>
+        <v>7194846</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -883,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113356288</v>
+        <v>113356484</v>
       </c>
       <c r="B4" t="n">
-        <v>90814</v>
+        <v>96361</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>3298</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -923,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>749589</v>
+        <v>749552</v>
       </c>
       <c r="R4" t="n">
-        <v>7194789</v>
+        <v>7194775</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113356484</v>
+        <v>113356593</v>
       </c>
       <c r="B5" t="n">
-        <v>96361</v>
+        <v>96355</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,23 +1009,19 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>221944</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lopplummer (aggregat)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1029,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>749552</v>
+        <v>749577</v>
       </c>
       <c r="R5" t="n">
-        <v>7194775</v>
+        <v>7194739</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Johanna Kühne, Anna Dahlin</t>
+          <t>Johanna Kühne, Anna Högdahl, Amanda Johansson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 51945-2022 artfynd.xlsx
+++ b/artfynd/A 51945-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
